--- a/detayli_imalat_maliyet_raporu.xlsx
+++ b/detayli_imalat_maliyet_raporu.xlsx
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ferforje Korkuluk</t>
+          <t>Ferforppje Korkuluk</t>
         </is>
       </c>
       <c r="B5" t="n">
